--- a/template/远建2026版三级计划（绿城基础含公式）.xlsx
+++ b/template/远建2026版三级计划（绿城基础含公式）.xlsx
@@ -4222,7 +4222,8 @@
       <c r="J25" s="54"/>
       <c r="K25" s="54"/>
       <c r="L25" s="54">
-        <v>44972.0</v>
+        <f>L6+70</f>
+        <v>44984.0</v>
       </c>
       <c r="M25" s="66" t="s">
         <v>98</v>

--- a/template/远建2026版三级计划（绿城基础含公式）.xlsx
+++ b/template/远建2026版三级计划（绿城基础含公式）.xlsx
@@ -3000,7 +3000,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8800,8 +8800,7 @@
       <c r="J116" s="68"/>
       <c r="K116" s="68"/>
       <c r="L116" s="68">
-        <f>IF(前置信息!$B$8&lt;8,'节点计划 (终稿)'!L100+150,'节点计划 (终稿)'!L100+170)</f>
-        <v>45596.0</v>
+        <f>IF(前置信息!$B$8&lt;8,'节点计划 (终稿)'!L100+100,'节点计划 (终稿)'!L100+100)</f>
       </c>
       <c r="M116" s="69" t="s">
         <v>371</v>
@@ -9106,8 +9105,7 @@
       <c r="J122" s="45"/>
       <c r="K122" s="45"/>
       <c r="L122" s="45">
-        <f>L133-40</f>
-        <v>45756.0</v>
+        <f>L133-25</f>
       </c>
       <c r="M122" s="43" t="s">
         <v>387</v>
@@ -9208,8 +9206,7 @@
       <c r="J124" s="45"/>
       <c r="K124" s="45"/>
       <c r="L124" s="45">
-        <f>L112+120</f>
-        <v>45746.0</v>
+        <f>L112+90</f>
       </c>
       <c r="M124" s="43" t="s">
         <v>392</v>
@@ -10204,8 +10201,7 @@
       <c r="J145" s="109"/>
       <c r="K145" s="109"/>
       <c r="L145" s="109">
-        <f>IF(前置信息!$B$10="精装",IF(前置信息!$B$8&lt;=11,'节点计划 (终稿)'!L100+14*30,'节点计划 (终稿)'!L100+15*30),IF(前置信息!$B$8&lt;=11,'节点计划 (终稿)'!L100+11*30,'节点计划 (终稿)'!L100+12*30))</f>
-        <v>45876.0</v>
+        <f>IF(前置信息!$B$10="精装",IF(前置信息!$B$8&lt;=11,IF(前置信息!$B$11="有",'节点计划 (终稿)'!L100+14*30+60,'节点计划 (终稿)'!L100+14*30),IF(前置信息!$B$11="有",'节点计划 (终稿)'!L100+15*30+60,'节点计划 (终稿)'!L100+15*30)),IF(前置信息!$B$8&lt;=11,IF(前置信息!$B$11="有",'节点计划 (终稿)'!L100+11*30+60,'节点计划 (终稿)'!L100+11*30),IF(前置信息!$B$11="有",'节点计划 (终稿)'!L100+12*30+60,'节点计划 (终稿)'!L100+12*30)))</f>
       </c>
       <c r="M145" s="66" t="s">
         <v>438</v>
